--- a/astro-site/public/dl/restaurant-schedule-templates/01-restaurant-schedule-template.xlsx
+++ b/astro-site/public/dl/restaurant-schedule-templates/01-restaurant-schedule-template.xlsx
@@ -887,7 +887,7 @@
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>▸ The "Monthly Schedule" sheet repeats the grid for five weeks (31-day months do not fit in four), inherits the names from the "Weekly Schedule", adds up each employee's total for the month and shows the weekly average, which is what you compare with their scheduled hours when you spread hours unevenly.</t>
+          <t>▸ The "Monthly Schedule" sheet repeats the grid for five weeks (31-day months do not fit in four), inherits the names from the "Weekly Schedule" and adds up each employee's total for the month. The weekly average is for planning only: under the FLSA each workweek stands alone — column J of each week is what counts. UK: the 48 h limit IS a 17-week average.</t>
         </is>
       </c>
     </row>
@@ -904,21 +904,21 @@
     <row r="12">
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>▸ K · Rest between shifts: compares the END time of each day with the START time of the next, counting the shift that crosses midnight. It fires below 10 h (the "clopening" rule of the Fair Workweek laws; UK: 11 h, Working Time Regulations reg. 10). The threshold is cell Shifts!B3.</t>
+          <t>▸ K · Rest between shifts: compares the END time of each day with the START time of the next, counting the shift that crosses midnight. It fires below 10 h, the "clopening" rule of predictive scheduling (Fair Workweek) laws. There is no federal rule: these are state or city laws (Oregon, Seattle, NYC, Chicago, Philadelphia and others), mostly for large chains. UK: 11 h, Working Time Regulations reg. 10. The threshold is cell Shifts!B3.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>▸ L · Weekly day off: federal law sets no mandatory day off. With zero days off in the week the alert is red; with one, amber (six days on: a 7th day in a row is premium pay in California, Labor Code §§551-552). UK: 24 h off per week (WTR reg. 11).</t>
+          <t>▸ L · Weekly day off: federal law sets no mandatory day off. With zero days off in the week the alert is red; with one, amber (six days on: work on a 7th consecutive day of the workweek is premium pay in California, Labor Code §510(a); §§551-552 give one day's rest in seven). UK: 24 h off per week (WTR reg. 11).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>▸ M · Weekly hours: compares with the maximum in column J (green, 40 by default, the FLSA overtime threshold), not with a fixed 40: for a part-timer, type their scheduled hours and the alerts fire at 20.</t>
+          <t>▸ M · Weekly hours: compares with the maximum in column J (green, 40 by default, the FLSA overtime threshold), not with a fixed 40: for a part-timer, type their scheduled hours and the alerts fire at 20. The grid runs Monday–Sunday, the same workweek as B3 of the "Time Log" in file 02 "Overtime Tracker &amp; Time Log" (2 = Monday). If your payroll week starts on another day, change B3 there and read this grid accordingly.</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
     <row r="16">
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>▸ O and P · Minors: type Y in column O (the alert in file 07 (Employee Directory &amp; Expiry Tracker) tells you as soon as you enter the date of birth). With Y, alert N drops to 8 h and P fires if you give them a NIGHT (N) or DOUBLE (DBL) shift. Child labor rules apply (29 CFR 570): under 16, 8 h on a non-school day and nothing after 7 PM (9 PM from June 1 to Labor Day); 16-17, no hazardous machines such as meat slicers and dough mixers. UK: young workers, 8 h a day, 40 h a week, no night work.</t>
+          <t>▸ O and P · Minors: type Y in column O for anyone under 18 (the alert in file 07 "Employee Directory &amp; Expiry Tracker" tells you as soon as you enter the date of birth). With Y, alert N drops to 8 h and P turns red on a NIGHT (N) or DOUBLE (DBL) shift and amber otherwise. The federal hour rules apply UNDER 16 (29 CFR 570.35): 8 h on a non-school day and no work after 7 PM (9 PM from June 1 to Labor Day), so a PM or SP shift that ends later is out too. For 16-17 there are no federal hour limits: check your state law (federal law bans only hazardous work such as meat slicers and dough mixers, 29 CFR 570.50-570.68). UK: young workers, 8 h a day, 40 h a week, no night work.</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="21">
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>▸ V (vacation / PTO) and S (sick) are marked here with the same letters as in file 05 (PTO &amp; Vacation Planner) and count 0 h. Holiday (H) and other leave (L) exist only in 05: in this schedule a day off is OFF.</t>
+          <t>▸ V (vacation / PTO) and S (sick) are marked here with the same letters as in file 05 "PTO &amp; Vacation Planner" and count 0 h. Holiday (H) and other leave (L) exist only in 05: in this schedule a day off is OFF.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
     <row r="15" ht="32" customHeight="1">
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t>Type times as clock times: 7:00 AM or 3:30 PM. Column A is not editable: those 8 codes are the ones in the schedule drop-down and in the calendar of file 05 (PTO &amp; Vacation Planner).</t>
+          <t>Type times as clock times: 7:00 AM or 3:30 PM. Column A is not editable: those 8 codes are the ones in the schedule drop-down and in the calendar of file 05 "PTO &amp; Vacation Planner".</t>
         </is>
       </c>
     </row>
@@ -1332,8 +1332,8 @@
     <mergeCell ref="B14:F14"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="B2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2 · max_shift_hours" prompt="Kit rule: federal law (FLSA) sets no daily maximum for adults. The alert fires above this many hours. Keep the rest between shifts either way."/>
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2 · min_rest_hours" prompt="Fair Workweek &quot;clopening&quot; rule: 10 hours between shifts (NYC fast food 11 h; UK 11 h under the Working Time Regulations). Type the rule that applies to you."/>
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Long-shift alert threshold" prompt="Kit rule: federal law (FLSA) sets no daily maximum for adults. The alert fires above this many hours. Keep the rest between shifts either way."/>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Minimum rest between shifts" prompt="Kit default 10 h: the &quot;clopening&quot; rule of predictive scheduling laws. No federal rule: they are state or city laws (Oregon, Seattle, NYC, Chicago, Philadelphia and others), mostly for large chains. UK: 11 h. Type the rule that applies to you."/>
     <dataValidation sqref="C5:D12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Type a time like 7:00 AM or 3:30 PM (not a plain 7)." prompt="Type a time like 7:00 AM or 3:30 PM (not a plain 7)." type="time" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>0.999305555555556</formula2>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="O5" s="27" t="inlineStr">
         <is>
-          <t>Minor (under 18) Y/N</t>
+          <t>Under 18? (Y/N)</t>
         </is>
       </c>
       <c r="P5" s="27" t="inlineStr">
@@ -1596,12 +1596,12 @@
         <v/>
       </c>
       <c r="N6">
-        <f>IF($O6="Y",IF(OR(IF($R6="",0,$R6)&gt;8,IF($S6="",0,$S6)&gt;8,IF($T6="",0,$T6)&gt;8,IF($U6="",0,$U6)&gt;8,IF($V6="",0,$V6)&gt;8,IF($W6="",0,$W6)&gt;8,IF($X6="",0,$X6)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R6="",0,$R6)&gt;Shifts!$B$2,IF($S6="",0,$S6)&gt;Shifts!$B$2,IF($T6="",0,$T6)&gt;Shifts!$B$2,IF($U6="",0,$U6)&gt;Shifts!$B$2,IF($V6="",0,$V6)&gt;Shifts!$B$2,IF($W6="",0,$W6)&gt;Shifts!$B$2,IF($X6="",0,$X6)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O6="Y",IF(OR(IF($R6="",0,$R6)&gt;8,IF($S6="",0,$S6)&gt;8,IF($T6="",0,$T6)&gt;8,IF($U6="",0,$U6)&gt;8,IF($V6="",0,$V6)&gt;8,IF($W6="",0,$W6)&gt;8,IF($X6="",0,$X6)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R6="",0,$R6)&gt;Shifts!$B$2,IF($S6="",0,$S6)&gt;Shifts!$B$2,IF($T6="",0,$T6)&gt;Shifts!$B$2,IF($U6="",0,$U6)&gt;Shifts!$B$2,IF($V6="",0,$V6)&gt;Shifts!$B$2,IF($W6="",0,$W6)&gt;Shifts!$B$2,IF($X6="",0,$X6)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O6" s="54" t="n"/>
       <c r="P6" s="55">
-        <f>IF($O6&lt;&gt;"Y","",IF(OR($B6="N",$B6="DBL",$C6="N",$C6="DBL",$D6="N",$D6="DBL",$E6="N",$E6="DBL",$F6="N",$F6="DBL",$G6="N",$G6="DBL",$H6="N",$H6="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O6&lt;&gt;"Y","",IF(OR($B6="N",$B6="DBL",$C6="N",$C6="DBL",$D6="N",$D6="DBL",$E6="N",$E6="DBL",$F6="N",$F6="DBL",$G6="N",$G6="DBL",$H6="N",$H6="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R6">
@@ -1742,12 +1742,12 @@
         <v/>
       </c>
       <c r="N7">
-        <f>IF($O7="Y",IF(OR(IF($R7="",0,$R7)&gt;8,IF($S7="",0,$S7)&gt;8,IF($T7="",0,$T7)&gt;8,IF($U7="",0,$U7)&gt;8,IF($V7="",0,$V7)&gt;8,IF($W7="",0,$W7)&gt;8,IF($X7="",0,$X7)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R7="",0,$R7)&gt;Shifts!$B$2,IF($S7="",0,$S7)&gt;Shifts!$B$2,IF($T7="",0,$T7)&gt;Shifts!$B$2,IF($U7="",0,$U7)&gt;Shifts!$B$2,IF($V7="",0,$V7)&gt;Shifts!$B$2,IF($W7="",0,$W7)&gt;Shifts!$B$2,IF($X7="",0,$X7)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O7="Y",IF(OR(IF($R7="",0,$R7)&gt;8,IF($S7="",0,$S7)&gt;8,IF($T7="",0,$T7)&gt;8,IF($U7="",0,$U7)&gt;8,IF($V7="",0,$V7)&gt;8,IF($W7="",0,$W7)&gt;8,IF($X7="",0,$X7)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R7="",0,$R7)&gt;Shifts!$B$2,IF($S7="",0,$S7)&gt;Shifts!$B$2,IF($T7="",0,$T7)&gt;Shifts!$B$2,IF($U7="",0,$U7)&gt;Shifts!$B$2,IF($V7="",0,$V7)&gt;Shifts!$B$2,IF($W7="",0,$W7)&gt;Shifts!$B$2,IF($X7="",0,$X7)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O7" s="54" t="n"/>
       <c r="P7" s="55">
-        <f>IF($O7&lt;&gt;"Y","",IF(OR($B7="N",$B7="DBL",$C7="N",$C7="DBL",$D7="N",$D7="DBL",$E7="N",$E7="DBL",$F7="N",$F7="DBL",$G7="N",$G7="DBL",$H7="N",$H7="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O7&lt;&gt;"Y","",IF(OR($B7="N",$B7="DBL",$C7="N",$C7="DBL",$D7="N",$D7="DBL",$E7="N",$E7="DBL",$F7="N",$F7="DBL",$G7="N",$G7="DBL",$H7="N",$H7="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R7">
@@ -1888,12 +1888,12 @@
         <v/>
       </c>
       <c r="N8">
-        <f>IF($O8="Y",IF(OR(IF($R8="",0,$R8)&gt;8,IF($S8="",0,$S8)&gt;8,IF($T8="",0,$T8)&gt;8,IF($U8="",0,$U8)&gt;8,IF($V8="",0,$V8)&gt;8,IF($W8="",0,$W8)&gt;8,IF($X8="",0,$X8)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R8="",0,$R8)&gt;Shifts!$B$2,IF($S8="",0,$S8)&gt;Shifts!$B$2,IF($T8="",0,$T8)&gt;Shifts!$B$2,IF($U8="",0,$U8)&gt;Shifts!$B$2,IF($V8="",0,$V8)&gt;Shifts!$B$2,IF($W8="",0,$W8)&gt;Shifts!$B$2,IF($X8="",0,$X8)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O8="Y",IF(OR(IF($R8="",0,$R8)&gt;8,IF($S8="",0,$S8)&gt;8,IF($T8="",0,$T8)&gt;8,IF($U8="",0,$U8)&gt;8,IF($V8="",0,$V8)&gt;8,IF($W8="",0,$W8)&gt;8,IF($X8="",0,$X8)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R8="",0,$R8)&gt;Shifts!$B$2,IF($S8="",0,$S8)&gt;Shifts!$B$2,IF($T8="",0,$T8)&gt;Shifts!$B$2,IF($U8="",0,$U8)&gt;Shifts!$B$2,IF($V8="",0,$V8)&gt;Shifts!$B$2,IF($W8="",0,$W8)&gt;Shifts!$B$2,IF($X8="",0,$X8)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O8" s="54" t="n"/>
       <c r="P8" s="55">
-        <f>IF($O8&lt;&gt;"Y","",IF(OR($B8="N",$B8="DBL",$C8="N",$C8="DBL",$D8="N",$D8="DBL",$E8="N",$E8="DBL",$F8="N",$F8="DBL",$G8="N",$G8="DBL",$H8="N",$H8="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O8&lt;&gt;"Y","",IF(OR($B8="N",$B8="DBL",$C8="N",$C8="DBL",$D8="N",$D8="DBL",$E8="N",$E8="DBL",$F8="N",$F8="DBL",$G8="N",$G8="DBL",$H8="N",$H8="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R8">
@@ -2034,12 +2034,12 @@
         <v/>
       </c>
       <c r="N9">
-        <f>IF($O9="Y",IF(OR(IF($R9="",0,$R9)&gt;8,IF($S9="",0,$S9)&gt;8,IF($T9="",0,$T9)&gt;8,IF($U9="",0,$U9)&gt;8,IF($V9="",0,$V9)&gt;8,IF($W9="",0,$W9)&gt;8,IF($X9="",0,$X9)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R9="",0,$R9)&gt;Shifts!$B$2,IF($S9="",0,$S9)&gt;Shifts!$B$2,IF($T9="",0,$T9)&gt;Shifts!$B$2,IF($U9="",0,$U9)&gt;Shifts!$B$2,IF($V9="",0,$V9)&gt;Shifts!$B$2,IF($W9="",0,$W9)&gt;Shifts!$B$2,IF($X9="",0,$X9)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O9="Y",IF(OR(IF($R9="",0,$R9)&gt;8,IF($S9="",0,$S9)&gt;8,IF($T9="",0,$T9)&gt;8,IF($U9="",0,$U9)&gt;8,IF($V9="",0,$V9)&gt;8,IF($W9="",0,$W9)&gt;8,IF($X9="",0,$X9)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R9="",0,$R9)&gt;Shifts!$B$2,IF($S9="",0,$S9)&gt;Shifts!$B$2,IF($T9="",0,$T9)&gt;Shifts!$B$2,IF($U9="",0,$U9)&gt;Shifts!$B$2,IF($V9="",0,$V9)&gt;Shifts!$B$2,IF($W9="",0,$W9)&gt;Shifts!$B$2,IF($X9="",0,$X9)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O9" s="54" t="n"/>
       <c r="P9" s="55">
-        <f>IF($O9&lt;&gt;"Y","",IF(OR($B9="N",$B9="DBL",$C9="N",$C9="DBL",$D9="N",$D9="DBL",$E9="N",$E9="DBL",$F9="N",$F9="DBL",$G9="N",$G9="DBL",$H9="N",$H9="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O9&lt;&gt;"Y","",IF(OR($B9="N",$B9="DBL",$C9="N",$C9="DBL",$D9="N",$D9="DBL",$E9="N",$E9="DBL",$F9="N",$F9="DBL",$G9="N",$G9="DBL",$H9="N",$H9="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R9">
@@ -2180,12 +2180,12 @@
         <v/>
       </c>
       <c r="N10">
-        <f>IF($O10="Y",IF(OR(IF($R10="",0,$R10)&gt;8,IF($S10="",0,$S10)&gt;8,IF($T10="",0,$T10)&gt;8,IF($U10="",0,$U10)&gt;8,IF($V10="",0,$V10)&gt;8,IF($W10="",0,$W10)&gt;8,IF($X10="",0,$X10)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R10="",0,$R10)&gt;Shifts!$B$2,IF($S10="",0,$S10)&gt;Shifts!$B$2,IF($T10="",0,$T10)&gt;Shifts!$B$2,IF($U10="",0,$U10)&gt;Shifts!$B$2,IF($V10="",0,$V10)&gt;Shifts!$B$2,IF($W10="",0,$W10)&gt;Shifts!$B$2,IF($X10="",0,$X10)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O10="Y",IF(OR(IF($R10="",0,$R10)&gt;8,IF($S10="",0,$S10)&gt;8,IF($T10="",0,$T10)&gt;8,IF($U10="",0,$U10)&gt;8,IF($V10="",0,$V10)&gt;8,IF($W10="",0,$W10)&gt;8,IF($X10="",0,$X10)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R10="",0,$R10)&gt;Shifts!$B$2,IF($S10="",0,$S10)&gt;Shifts!$B$2,IF($T10="",0,$T10)&gt;Shifts!$B$2,IF($U10="",0,$U10)&gt;Shifts!$B$2,IF($V10="",0,$V10)&gt;Shifts!$B$2,IF($W10="",0,$W10)&gt;Shifts!$B$2,IF($X10="",0,$X10)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O10" s="54" t="n"/>
       <c r="P10" s="55">
-        <f>IF($O10&lt;&gt;"Y","",IF(OR($B10="N",$B10="DBL",$C10="N",$C10="DBL",$D10="N",$D10="DBL",$E10="N",$E10="DBL",$F10="N",$F10="DBL",$G10="N",$G10="DBL",$H10="N",$H10="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O10&lt;&gt;"Y","",IF(OR($B10="N",$B10="DBL",$C10="N",$C10="DBL",$D10="N",$D10="DBL",$E10="N",$E10="DBL",$F10="N",$F10="DBL",$G10="N",$G10="DBL",$H10="N",$H10="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R10">
@@ -2326,12 +2326,12 @@
         <v/>
       </c>
       <c r="N11">
-        <f>IF($O11="Y",IF(OR(IF($R11="",0,$R11)&gt;8,IF($S11="",0,$S11)&gt;8,IF($T11="",0,$T11)&gt;8,IF($U11="",0,$U11)&gt;8,IF($V11="",0,$V11)&gt;8,IF($W11="",0,$W11)&gt;8,IF($X11="",0,$X11)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R11="",0,$R11)&gt;Shifts!$B$2,IF($S11="",0,$S11)&gt;Shifts!$B$2,IF($T11="",0,$T11)&gt;Shifts!$B$2,IF($U11="",0,$U11)&gt;Shifts!$B$2,IF($V11="",0,$V11)&gt;Shifts!$B$2,IF($W11="",0,$W11)&gt;Shifts!$B$2,IF($X11="",0,$X11)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O11="Y",IF(OR(IF($R11="",0,$R11)&gt;8,IF($S11="",0,$S11)&gt;8,IF($T11="",0,$T11)&gt;8,IF($U11="",0,$U11)&gt;8,IF($V11="",0,$V11)&gt;8,IF($W11="",0,$W11)&gt;8,IF($X11="",0,$X11)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R11="",0,$R11)&gt;Shifts!$B$2,IF($S11="",0,$S11)&gt;Shifts!$B$2,IF($T11="",0,$T11)&gt;Shifts!$B$2,IF($U11="",0,$U11)&gt;Shifts!$B$2,IF($V11="",0,$V11)&gt;Shifts!$B$2,IF($W11="",0,$W11)&gt;Shifts!$B$2,IF($X11="",0,$X11)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O11" s="54" t="n"/>
       <c r="P11" s="55">
-        <f>IF($O11&lt;&gt;"Y","",IF(OR($B11="N",$B11="DBL",$C11="N",$C11="DBL",$D11="N",$D11="DBL",$E11="N",$E11="DBL",$F11="N",$F11="DBL",$G11="N",$G11="DBL",$H11="N",$H11="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O11&lt;&gt;"Y","",IF(OR($B11="N",$B11="DBL",$C11="N",$C11="DBL",$D11="N",$D11="DBL",$E11="N",$E11="DBL",$F11="N",$F11="DBL",$G11="N",$G11="DBL",$H11="N",$H11="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R11">
@@ -2472,12 +2472,12 @@
         <v/>
       </c>
       <c r="N12">
-        <f>IF($O12="Y",IF(OR(IF($R12="",0,$R12)&gt;8,IF($S12="",0,$S12)&gt;8,IF($T12="",0,$T12)&gt;8,IF($U12="",0,$U12)&gt;8,IF($V12="",0,$V12)&gt;8,IF($W12="",0,$W12)&gt;8,IF($X12="",0,$X12)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R12="",0,$R12)&gt;Shifts!$B$2,IF($S12="",0,$S12)&gt;Shifts!$B$2,IF($T12="",0,$T12)&gt;Shifts!$B$2,IF($U12="",0,$U12)&gt;Shifts!$B$2,IF($V12="",0,$V12)&gt;Shifts!$B$2,IF($W12="",0,$W12)&gt;Shifts!$B$2,IF($X12="",0,$X12)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O12="Y",IF(OR(IF($R12="",0,$R12)&gt;8,IF($S12="",0,$S12)&gt;8,IF($T12="",0,$T12)&gt;8,IF($U12="",0,$U12)&gt;8,IF($V12="",0,$V12)&gt;8,IF($W12="",0,$W12)&gt;8,IF($X12="",0,$X12)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R12="",0,$R12)&gt;Shifts!$B$2,IF($S12="",0,$S12)&gt;Shifts!$B$2,IF($T12="",0,$T12)&gt;Shifts!$B$2,IF($U12="",0,$U12)&gt;Shifts!$B$2,IF($V12="",0,$V12)&gt;Shifts!$B$2,IF($W12="",0,$W12)&gt;Shifts!$B$2,IF($X12="",0,$X12)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O12" s="54" t="n"/>
       <c r="P12" s="55">
-        <f>IF($O12&lt;&gt;"Y","",IF(OR($B12="N",$B12="DBL",$C12="N",$C12="DBL",$D12="N",$D12="DBL",$E12="N",$E12="DBL",$F12="N",$F12="DBL",$G12="N",$G12="DBL",$H12="N",$H12="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O12&lt;&gt;"Y","",IF(OR($B12="N",$B12="DBL",$C12="N",$C12="DBL",$D12="N",$D12="DBL",$E12="N",$E12="DBL",$F12="N",$F12="DBL",$G12="N",$G12="DBL",$H12="N",$H12="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R12">
@@ -2618,12 +2618,12 @@
         <v/>
       </c>
       <c r="N13">
-        <f>IF($O13="Y",IF(OR(IF($R13="",0,$R13)&gt;8,IF($S13="",0,$S13)&gt;8,IF($T13="",0,$T13)&gt;8,IF($U13="",0,$U13)&gt;8,IF($V13="",0,$V13)&gt;8,IF($W13="",0,$W13)&gt;8,IF($X13="",0,$X13)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R13="",0,$R13)&gt;Shifts!$B$2,IF($S13="",0,$S13)&gt;Shifts!$B$2,IF($T13="",0,$T13)&gt;Shifts!$B$2,IF($U13="",0,$U13)&gt;Shifts!$B$2,IF($V13="",0,$V13)&gt;Shifts!$B$2,IF($W13="",0,$W13)&gt;Shifts!$B$2,IF($X13="",0,$X13)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O13="Y",IF(OR(IF($R13="",0,$R13)&gt;8,IF($S13="",0,$S13)&gt;8,IF($T13="",0,$T13)&gt;8,IF($U13="",0,$U13)&gt;8,IF($V13="",0,$V13)&gt;8,IF($W13="",0,$W13)&gt;8,IF($X13="",0,$X13)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R13="",0,$R13)&gt;Shifts!$B$2,IF($S13="",0,$S13)&gt;Shifts!$B$2,IF($T13="",0,$T13)&gt;Shifts!$B$2,IF($U13="",0,$U13)&gt;Shifts!$B$2,IF($V13="",0,$V13)&gt;Shifts!$B$2,IF($W13="",0,$W13)&gt;Shifts!$B$2,IF($X13="",0,$X13)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O13" s="54" t="n"/>
       <c r="P13" s="55">
-        <f>IF($O13&lt;&gt;"Y","",IF(OR($B13="N",$B13="DBL",$C13="N",$C13="DBL",$D13="N",$D13="DBL",$E13="N",$E13="DBL",$F13="N",$F13="DBL",$G13="N",$G13="DBL",$H13="N",$H13="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O13&lt;&gt;"Y","",IF(OR($B13="N",$B13="DBL",$C13="N",$C13="DBL",$D13="N",$D13="DBL",$E13="N",$E13="DBL",$F13="N",$F13="DBL",$G13="N",$G13="DBL",$H13="N",$H13="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R13">
@@ -2764,12 +2764,12 @@
         <v/>
       </c>
       <c r="N14">
-        <f>IF($O14="Y",IF(OR(IF($R14="",0,$R14)&gt;8,IF($S14="",0,$S14)&gt;8,IF($T14="",0,$T14)&gt;8,IF($U14="",0,$U14)&gt;8,IF($V14="",0,$V14)&gt;8,IF($W14="",0,$W14)&gt;8,IF($X14="",0,$X14)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R14="",0,$R14)&gt;Shifts!$B$2,IF($S14="",0,$S14)&gt;Shifts!$B$2,IF($T14="",0,$T14)&gt;Shifts!$B$2,IF($U14="",0,$U14)&gt;Shifts!$B$2,IF($V14="",0,$V14)&gt;Shifts!$B$2,IF($W14="",0,$W14)&gt;Shifts!$B$2,IF($X14="",0,$X14)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O14="Y",IF(OR(IF($R14="",0,$R14)&gt;8,IF($S14="",0,$S14)&gt;8,IF($T14="",0,$T14)&gt;8,IF($U14="",0,$U14)&gt;8,IF($V14="",0,$V14)&gt;8,IF($W14="",0,$W14)&gt;8,IF($X14="",0,$X14)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R14="",0,$R14)&gt;Shifts!$B$2,IF($S14="",0,$S14)&gt;Shifts!$B$2,IF($T14="",0,$T14)&gt;Shifts!$B$2,IF($U14="",0,$U14)&gt;Shifts!$B$2,IF($V14="",0,$V14)&gt;Shifts!$B$2,IF($W14="",0,$W14)&gt;Shifts!$B$2,IF($X14="",0,$X14)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O14" s="54" t="n"/>
       <c r="P14" s="55">
-        <f>IF($O14&lt;&gt;"Y","",IF(OR($B14="N",$B14="DBL",$C14="N",$C14="DBL",$D14="N",$D14="DBL",$E14="N",$E14="DBL",$F14="N",$F14="DBL",$G14="N",$G14="DBL",$H14="N",$H14="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O14&lt;&gt;"Y","",IF(OR($B14="N",$B14="DBL",$C14="N",$C14="DBL",$D14="N",$D14="DBL",$E14="N",$E14="DBL",$F14="N",$F14="DBL",$G14="N",$G14="DBL",$H14="N",$H14="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R14">
@@ -2910,12 +2910,12 @@
         <v/>
       </c>
       <c r="N15">
-        <f>IF($O15="Y",IF(OR(IF($R15="",0,$R15)&gt;8,IF($S15="",0,$S15)&gt;8,IF($T15="",0,$T15)&gt;8,IF($U15="",0,$U15)&gt;8,IF($V15="",0,$V15)&gt;8,IF($W15="",0,$W15)&gt;8,IF($X15="",0,$X15)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R15="",0,$R15)&gt;Shifts!$B$2,IF($S15="",0,$S15)&gt;Shifts!$B$2,IF($T15="",0,$T15)&gt;Shifts!$B$2,IF($U15="",0,$U15)&gt;Shifts!$B$2,IF($V15="",0,$V15)&gt;Shifts!$B$2,IF($W15="",0,$W15)&gt;Shifts!$B$2,IF($X15="",0,$X15)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O15="Y",IF(OR(IF($R15="",0,$R15)&gt;8,IF($S15="",0,$S15)&gt;8,IF($T15="",0,$T15)&gt;8,IF($U15="",0,$U15)&gt;8,IF($V15="",0,$V15)&gt;8,IF($W15="",0,$W15)&gt;8,IF($X15="",0,$X15)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R15="",0,$R15)&gt;Shifts!$B$2,IF($S15="",0,$S15)&gt;Shifts!$B$2,IF($T15="",0,$T15)&gt;Shifts!$B$2,IF($U15="",0,$U15)&gt;Shifts!$B$2,IF($V15="",0,$V15)&gt;Shifts!$B$2,IF($W15="",0,$W15)&gt;Shifts!$B$2,IF($X15="",0,$X15)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O15" s="54" t="n"/>
       <c r="P15" s="55">
-        <f>IF($O15&lt;&gt;"Y","",IF(OR($B15="N",$B15="DBL",$C15="N",$C15="DBL",$D15="N",$D15="DBL",$E15="N",$E15="DBL",$F15="N",$F15="DBL",$G15="N",$G15="DBL",$H15="N",$H15="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O15&lt;&gt;"Y","",IF(OR($B15="N",$B15="DBL",$C15="N",$C15="DBL",$D15="N",$D15="DBL",$E15="N",$E15="DBL",$F15="N",$F15="DBL",$G15="N",$G15="DBL",$H15="N",$H15="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R15">
@@ -3056,12 +3056,12 @@
         <v/>
       </c>
       <c r="N16">
-        <f>IF($O16="Y",IF(OR(IF($R16="",0,$R16)&gt;8,IF($S16="",0,$S16)&gt;8,IF($T16="",0,$T16)&gt;8,IF($U16="",0,$U16)&gt;8,IF($V16="",0,$V16)&gt;8,IF($W16="",0,$W16)&gt;8,IF($X16="",0,$X16)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R16="",0,$R16)&gt;Shifts!$B$2,IF($S16="",0,$S16)&gt;Shifts!$B$2,IF($T16="",0,$T16)&gt;Shifts!$B$2,IF($U16="",0,$U16)&gt;Shifts!$B$2,IF($V16="",0,$V16)&gt;Shifts!$B$2,IF($W16="",0,$W16)&gt;Shifts!$B$2,IF($X16="",0,$X16)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O16="Y",IF(OR(IF($R16="",0,$R16)&gt;8,IF($S16="",0,$S16)&gt;8,IF($T16="",0,$T16)&gt;8,IF($U16="",0,$U16)&gt;8,IF($V16="",0,$V16)&gt;8,IF($W16="",0,$W16)&gt;8,IF($X16="",0,$X16)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R16="",0,$R16)&gt;Shifts!$B$2,IF($S16="",0,$S16)&gt;Shifts!$B$2,IF($T16="",0,$T16)&gt;Shifts!$B$2,IF($U16="",0,$U16)&gt;Shifts!$B$2,IF($V16="",0,$V16)&gt;Shifts!$B$2,IF($W16="",0,$W16)&gt;Shifts!$B$2,IF($X16="",0,$X16)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O16" s="54" t="n"/>
       <c r="P16" s="55">
-        <f>IF($O16&lt;&gt;"Y","",IF(OR($B16="N",$B16="DBL",$C16="N",$C16="DBL",$D16="N",$D16="DBL",$E16="N",$E16="DBL",$F16="N",$F16="DBL",$G16="N",$G16="DBL",$H16="N",$H16="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O16&lt;&gt;"Y","",IF(OR($B16="N",$B16="DBL",$C16="N",$C16="DBL",$D16="N",$D16="DBL",$E16="N",$E16="DBL",$F16="N",$F16="DBL",$G16="N",$G16="DBL",$H16="N",$H16="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R16">
@@ -3202,12 +3202,12 @@
         <v/>
       </c>
       <c r="N17">
-        <f>IF($O17="Y",IF(OR(IF($R17="",0,$R17)&gt;8,IF($S17="",0,$S17)&gt;8,IF($T17="",0,$T17)&gt;8,IF($U17="",0,$U17)&gt;8,IF($V17="",0,$V17)&gt;8,IF($W17="",0,$W17)&gt;8,IF($X17="",0,$X17)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R17="",0,$R17)&gt;Shifts!$B$2,IF($S17="",0,$S17)&gt;Shifts!$B$2,IF($T17="",0,$T17)&gt;Shifts!$B$2,IF($U17="",0,$U17)&gt;Shifts!$B$2,IF($V17="",0,$V17)&gt;Shifts!$B$2,IF($W17="",0,$W17)&gt;Shifts!$B$2,IF($X17="",0,$X17)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O17="Y",IF(OR(IF($R17="",0,$R17)&gt;8,IF($S17="",0,$S17)&gt;8,IF($T17="",0,$T17)&gt;8,IF($U17="",0,$U17)&gt;8,IF($V17="",0,$V17)&gt;8,IF($W17="",0,$W17)&gt;8,IF($X17="",0,$X17)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R17="",0,$R17)&gt;Shifts!$B$2,IF($S17="",0,$S17)&gt;Shifts!$B$2,IF($T17="",0,$T17)&gt;Shifts!$B$2,IF($U17="",0,$U17)&gt;Shifts!$B$2,IF($V17="",0,$V17)&gt;Shifts!$B$2,IF($W17="",0,$W17)&gt;Shifts!$B$2,IF($X17="",0,$X17)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O17" s="54" t="n"/>
       <c r="P17" s="55">
-        <f>IF($O17&lt;&gt;"Y","",IF(OR($B17="N",$B17="DBL",$C17="N",$C17="DBL",$D17="N",$D17="DBL",$E17="N",$E17="DBL",$F17="N",$F17="DBL",$G17="N",$G17="DBL",$H17="N",$H17="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O17&lt;&gt;"Y","",IF(OR($B17="N",$B17="DBL",$C17="N",$C17="DBL",$D17="N",$D17="DBL",$E17="N",$E17="DBL",$F17="N",$F17="DBL",$G17="N",$G17="DBL",$H17="N",$H17="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R17">
@@ -3348,12 +3348,12 @@
         <v/>
       </c>
       <c r="N18">
-        <f>IF($O18="Y",IF(OR(IF($R18="",0,$R18)&gt;8,IF($S18="",0,$S18)&gt;8,IF($T18="",0,$T18)&gt;8,IF($U18="",0,$U18)&gt;8,IF($V18="",0,$V18)&gt;8,IF($W18="",0,$W18)&gt;8,IF($X18="",0,$X18)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R18="",0,$R18)&gt;Shifts!$B$2,IF($S18="",0,$S18)&gt;Shifts!$B$2,IF($T18="",0,$T18)&gt;Shifts!$B$2,IF($U18="",0,$U18)&gt;Shifts!$B$2,IF($V18="",0,$V18)&gt;Shifts!$B$2,IF($W18="",0,$W18)&gt;Shifts!$B$2,IF($X18="",0,$X18)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O18="Y",IF(OR(IF($R18="",0,$R18)&gt;8,IF($S18="",0,$S18)&gt;8,IF($T18="",0,$T18)&gt;8,IF($U18="",0,$U18)&gt;8,IF($V18="",0,$V18)&gt;8,IF($W18="",0,$W18)&gt;8,IF($X18="",0,$X18)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R18="",0,$R18)&gt;Shifts!$B$2,IF($S18="",0,$S18)&gt;Shifts!$B$2,IF($T18="",0,$T18)&gt;Shifts!$B$2,IF($U18="",0,$U18)&gt;Shifts!$B$2,IF($V18="",0,$V18)&gt;Shifts!$B$2,IF($W18="",0,$W18)&gt;Shifts!$B$2,IF($X18="",0,$X18)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O18" s="54" t="n"/>
       <c r="P18" s="55">
-        <f>IF($O18&lt;&gt;"Y","",IF(OR($B18="N",$B18="DBL",$C18="N",$C18="DBL",$D18="N",$D18="DBL",$E18="N",$E18="DBL",$F18="N",$F18="DBL",$G18="N",$G18="DBL",$H18="N",$H18="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O18&lt;&gt;"Y","",IF(OR($B18="N",$B18="DBL",$C18="N",$C18="DBL",$D18="N",$D18="DBL",$E18="N",$E18="DBL",$F18="N",$F18="DBL",$G18="N",$G18="DBL",$H18="N",$H18="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R18">
@@ -3494,12 +3494,12 @@
         <v/>
       </c>
       <c r="N19">
-        <f>IF($O19="Y",IF(OR(IF($R19="",0,$R19)&gt;8,IF($S19="",0,$S19)&gt;8,IF($T19="",0,$T19)&gt;8,IF($U19="",0,$U19)&gt;8,IF($V19="",0,$V19)&gt;8,IF($W19="",0,$W19)&gt;8,IF($X19="",0,$X19)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R19="",0,$R19)&gt;Shifts!$B$2,IF($S19="",0,$S19)&gt;Shifts!$B$2,IF($T19="",0,$T19)&gt;Shifts!$B$2,IF($U19="",0,$U19)&gt;Shifts!$B$2,IF($V19="",0,$V19)&gt;Shifts!$B$2,IF($W19="",0,$W19)&gt;Shifts!$B$2,IF($X19="",0,$X19)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O19="Y",IF(OR(IF($R19="",0,$R19)&gt;8,IF($S19="",0,$S19)&gt;8,IF($T19="",0,$T19)&gt;8,IF($U19="",0,$U19)&gt;8,IF($V19="",0,$V19)&gt;8,IF($W19="",0,$W19)&gt;8,IF($X19="",0,$X19)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R19="",0,$R19)&gt;Shifts!$B$2,IF($S19="",0,$S19)&gt;Shifts!$B$2,IF($T19="",0,$T19)&gt;Shifts!$B$2,IF($U19="",0,$U19)&gt;Shifts!$B$2,IF($V19="",0,$V19)&gt;Shifts!$B$2,IF($W19="",0,$W19)&gt;Shifts!$B$2,IF($X19="",0,$X19)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O19" s="54" t="n"/>
       <c r="P19" s="55">
-        <f>IF($O19&lt;&gt;"Y","",IF(OR($B19="N",$B19="DBL",$C19="N",$C19="DBL",$D19="N",$D19="DBL",$E19="N",$E19="DBL",$F19="N",$F19="DBL",$G19="N",$G19="DBL",$H19="N",$H19="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O19&lt;&gt;"Y","",IF(OR($B19="N",$B19="DBL",$C19="N",$C19="DBL",$D19="N",$D19="DBL",$E19="N",$E19="DBL",$F19="N",$F19="DBL",$G19="N",$G19="DBL",$H19="N",$H19="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R19">
@@ -3640,12 +3640,12 @@
         <v/>
       </c>
       <c r="N20">
-        <f>IF($O20="Y",IF(OR(IF($R20="",0,$R20)&gt;8,IF($S20="",0,$S20)&gt;8,IF($T20="",0,$T20)&gt;8,IF($U20="",0,$U20)&gt;8,IF($V20="",0,$V20)&gt;8,IF($W20="",0,$W20)&gt;8,IF($X20="",0,$X20)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R20="",0,$R20)&gt;Shifts!$B$2,IF($S20="",0,$S20)&gt;Shifts!$B$2,IF($T20="",0,$T20)&gt;Shifts!$B$2,IF($U20="",0,$U20)&gt;Shifts!$B$2,IF($V20="",0,$V20)&gt;Shifts!$B$2,IF($W20="",0,$W20)&gt;Shifts!$B$2,IF($X20="",0,$X20)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O20="Y",IF(OR(IF($R20="",0,$R20)&gt;8,IF($S20="",0,$S20)&gt;8,IF($T20="",0,$T20)&gt;8,IF($U20="",0,$U20)&gt;8,IF($V20="",0,$V20)&gt;8,IF($W20="",0,$W20)&gt;8,IF($X20="",0,$X20)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R20="",0,$R20)&gt;Shifts!$B$2,IF($S20="",0,$S20)&gt;Shifts!$B$2,IF($T20="",0,$T20)&gt;Shifts!$B$2,IF($U20="",0,$U20)&gt;Shifts!$B$2,IF($V20="",0,$V20)&gt;Shifts!$B$2,IF($W20="",0,$W20)&gt;Shifts!$B$2,IF($X20="",0,$X20)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O20" s="54" t="n"/>
       <c r="P20" s="55">
-        <f>IF($O20&lt;&gt;"Y","",IF(OR($B20="N",$B20="DBL",$C20="N",$C20="DBL",$D20="N",$D20="DBL",$E20="N",$E20="DBL",$F20="N",$F20="DBL",$G20="N",$G20="DBL",$H20="N",$H20="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O20&lt;&gt;"Y","",IF(OR($B20="N",$B20="DBL",$C20="N",$C20="DBL",$D20="N",$D20="DBL",$E20="N",$E20="DBL",$F20="N",$F20="DBL",$G20="N",$G20="DBL",$H20="N",$H20="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R20">
@@ -3786,12 +3786,12 @@
         <v/>
       </c>
       <c r="N21">
-        <f>IF($O21="Y",IF(OR(IF($R21="",0,$R21)&gt;8,IF($S21="",0,$S21)&gt;8,IF($T21="",0,$T21)&gt;8,IF($U21="",0,$U21)&gt;8,IF($V21="",0,$V21)&gt;8,IF($W21="",0,$W21)&gt;8,IF($X21="",0,$X21)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R21="",0,$R21)&gt;Shifts!$B$2,IF($S21="",0,$S21)&gt;Shifts!$B$2,IF($T21="",0,$T21)&gt;Shifts!$B$2,IF($U21="",0,$U21)&gt;Shifts!$B$2,IF($V21="",0,$V21)&gt;Shifts!$B$2,IF($W21="",0,$W21)&gt;Shifts!$B$2,IF($X21="",0,$X21)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O21="Y",IF(OR(IF($R21="",0,$R21)&gt;8,IF($S21="",0,$S21)&gt;8,IF($T21="",0,$T21)&gt;8,IF($U21="",0,$U21)&gt;8,IF($V21="",0,$V21)&gt;8,IF($W21="",0,$W21)&gt;8,IF($X21="",0,$X21)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R21="",0,$R21)&gt;Shifts!$B$2,IF($S21="",0,$S21)&gt;Shifts!$B$2,IF($T21="",0,$T21)&gt;Shifts!$B$2,IF($U21="",0,$U21)&gt;Shifts!$B$2,IF($V21="",0,$V21)&gt;Shifts!$B$2,IF($W21="",0,$W21)&gt;Shifts!$B$2,IF($X21="",0,$X21)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O21" s="54" t="n"/>
       <c r="P21" s="55">
-        <f>IF($O21&lt;&gt;"Y","",IF(OR($B21="N",$B21="DBL",$C21="N",$C21="DBL",$D21="N",$D21="DBL",$E21="N",$E21="DBL",$F21="N",$F21="DBL",$G21="N",$G21="DBL",$H21="N",$H21="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O21&lt;&gt;"Y","",IF(OR($B21="N",$B21="DBL",$C21="N",$C21="DBL",$D21="N",$D21="DBL",$E21="N",$E21="DBL",$F21="N",$F21="DBL",$G21="N",$G21="DBL",$H21="N",$H21="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R21">
@@ -3932,12 +3932,12 @@
         <v/>
       </c>
       <c r="N22">
-        <f>IF($O22="Y",IF(OR(IF($R22="",0,$R22)&gt;8,IF($S22="",0,$S22)&gt;8,IF($T22="",0,$T22)&gt;8,IF($U22="",0,$U22)&gt;8,IF($V22="",0,$V22)&gt;8,IF($W22="",0,$W22)&gt;8,IF($X22="",0,$X22)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R22="",0,$R22)&gt;Shifts!$B$2,IF($S22="",0,$S22)&gt;Shifts!$B$2,IF($T22="",0,$T22)&gt;Shifts!$B$2,IF($U22="",0,$U22)&gt;Shifts!$B$2,IF($V22="",0,$V22)&gt;Shifts!$B$2,IF($W22="",0,$W22)&gt;Shifts!$B$2,IF($X22="",0,$X22)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O22="Y",IF(OR(IF($R22="",0,$R22)&gt;8,IF($S22="",0,$S22)&gt;8,IF($T22="",0,$T22)&gt;8,IF($U22="",0,$U22)&gt;8,IF($V22="",0,$V22)&gt;8,IF($W22="",0,$W22)&gt;8,IF($X22="",0,$X22)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R22="",0,$R22)&gt;Shifts!$B$2,IF($S22="",0,$S22)&gt;Shifts!$B$2,IF($T22="",0,$T22)&gt;Shifts!$B$2,IF($U22="",0,$U22)&gt;Shifts!$B$2,IF($V22="",0,$V22)&gt;Shifts!$B$2,IF($W22="",0,$W22)&gt;Shifts!$B$2,IF($X22="",0,$X22)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O22" s="54" t="n"/>
       <c r="P22" s="55">
-        <f>IF($O22&lt;&gt;"Y","",IF(OR($B22="N",$B22="DBL",$C22="N",$C22="DBL",$D22="N",$D22="DBL",$E22="N",$E22="DBL",$F22="N",$F22="DBL",$G22="N",$G22="DBL",$H22="N",$H22="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O22&lt;&gt;"Y","",IF(OR($B22="N",$B22="DBL",$C22="N",$C22="DBL",$D22="N",$D22="DBL",$E22="N",$E22="DBL",$F22="N",$F22="DBL",$G22="N",$G22="DBL",$H22="N",$H22="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R22">
@@ -4078,12 +4078,12 @@
         <v/>
       </c>
       <c r="N23">
-        <f>IF($O23="Y",IF(OR(IF($R23="",0,$R23)&gt;8,IF($S23="",0,$S23)&gt;8,IF($T23="",0,$T23)&gt;8,IF($U23="",0,$U23)&gt;8,IF($V23="",0,$V23)&gt;8,IF($W23="",0,$W23)&gt;8,IF($X23="",0,$X23)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R23="",0,$R23)&gt;Shifts!$B$2,IF($S23="",0,$S23)&gt;Shifts!$B$2,IF($T23="",0,$T23)&gt;Shifts!$B$2,IF($U23="",0,$U23)&gt;Shifts!$B$2,IF($V23="",0,$V23)&gt;Shifts!$B$2,IF($W23="",0,$W23)&gt;Shifts!$B$2,IF($X23="",0,$X23)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O23="Y",IF(OR(IF($R23="",0,$R23)&gt;8,IF($S23="",0,$S23)&gt;8,IF($T23="",0,$T23)&gt;8,IF($U23="",0,$U23)&gt;8,IF($V23="",0,$V23)&gt;8,IF($W23="",0,$W23)&gt;8,IF($X23="",0,$X23)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R23="",0,$R23)&gt;Shifts!$B$2,IF($S23="",0,$S23)&gt;Shifts!$B$2,IF($T23="",0,$T23)&gt;Shifts!$B$2,IF($U23="",0,$U23)&gt;Shifts!$B$2,IF($V23="",0,$V23)&gt;Shifts!$B$2,IF($W23="",0,$W23)&gt;Shifts!$B$2,IF($X23="",0,$X23)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O23" s="54" t="n"/>
       <c r="P23" s="55">
-        <f>IF($O23&lt;&gt;"Y","",IF(OR($B23="N",$B23="DBL",$C23="N",$C23="DBL",$D23="N",$D23="DBL",$E23="N",$E23="DBL",$F23="N",$F23="DBL",$G23="N",$G23="DBL",$H23="N",$H23="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O23&lt;&gt;"Y","",IF(OR($B23="N",$B23="DBL",$C23="N",$C23="DBL",$D23="N",$D23="DBL",$E23="N",$E23="DBL",$F23="N",$F23="DBL",$G23="N",$G23="DBL",$H23="N",$H23="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R23">
@@ -4224,12 +4224,12 @@
         <v/>
       </c>
       <c r="N24">
-        <f>IF($O24="Y",IF(OR(IF($R24="",0,$R24)&gt;8,IF($S24="",0,$S24)&gt;8,IF($T24="",0,$T24)&gt;8,IF($U24="",0,$U24)&gt;8,IF($V24="",0,$V24)&gt;8,IF($W24="",0,$W24)&gt;8,IF($X24="",0,$X24)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R24="",0,$R24)&gt;Shifts!$B$2,IF($S24="",0,$S24)&gt;Shifts!$B$2,IF($T24="",0,$T24)&gt;Shifts!$B$2,IF($U24="",0,$U24)&gt;Shifts!$B$2,IF($V24="",0,$V24)&gt;Shifts!$B$2,IF($W24="",0,$W24)&gt;Shifts!$B$2,IF($X24="",0,$X24)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O24="Y",IF(OR(IF($R24="",0,$R24)&gt;8,IF($S24="",0,$S24)&gt;8,IF($T24="",0,$T24)&gt;8,IF($U24="",0,$U24)&gt;8,IF($V24="",0,$V24)&gt;8,IF($W24="",0,$W24)&gt;8,IF($X24="",0,$X24)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R24="",0,$R24)&gt;Shifts!$B$2,IF($S24="",0,$S24)&gt;Shifts!$B$2,IF($T24="",0,$T24)&gt;Shifts!$B$2,IF($U24="",0,$U24)&gt;Shifts!$B$2,IF($V24="",0,$V24)&gt;Shifts!$B$2,IF($W24="",0,$W24)&gt;Shifts!$B$2,IF($X24="",0,$X24)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O24" s="54" t="n"/>
       <c r="P24" s="55">
-        <f>IF($O24&lt;&gt;"Y","",IF(OR($B24="N",$B24="DBL",$C24="N",$C24="DBL",$D24="N",$D24="DBL",$E24="N",$E24="DBL",$F24="N",$F24="DBL",$G24="N",$G24="DBL",$H24="N",$H24="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O24&lt;&gt;"Y","",IF(OR($B24="N",$B24="DBL",$C24="N",$C24="DBL",$D24="N",$D24="DBL",$E24="N",$E24="DBL",$F24="N",$F24="DBL",$G24="N",$G24="DBL",$H24="N",$H24="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R24">
@@ -4370,12 +4370,12 @@
         <v/>
       </c>
       <c r="N25">
-        <f>IF($O25="Y",IF(OR(IF($R25="",0,$R25)&gt;8,IF($S25="",0,$S25)&gt;8,IF($T25="",0,$T25)&gt;8,IF($U25="",0,$U25)&gt;8,IF($V25="",0,$V25)&gt;8,IF($W25="",0,$W25)&gt;8,IF($X25="",0,$X25)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R25="",0,$R25)&gt;Shifts!$B$2,IF($S25="",0,$S25)&gt;Shifts!$B$2,IF($T25="",0,$T25)&gt;Shifts!$B$2,IF($U25="",0,$U25)&gt;Shifts!$B$2,IF($V25="",0,$V25)&gt;Shifts!$B$2,IF($W25="",0,$W25)&gt;Shifts!$B$2,IF($X25="",0,$X25)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O25="Y",IF(OR(IF($R25="",0,$R25)&gt;8,IF($S25="",0,$S25)&gt;8,IF($T25="",0,$T25)&gt;8,IF($U25="",0,$U25)&gt;8,IF($V25="",0,$V25)&gt;8,IF($W25="",0,$W25)&gt;8,IF($X25="",0,$X25)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R25="",0,$R25)&gt;Shifts!$B$2,IF($S25="",0,$S25)&gt;Shifts!$B$2,IF($T25="",0,$T25)&gt;Shifts!$B$2,IF($U25="",0,$U25)&gt;Shifts!$B$2,IF($V25="",0,$V25)&gt;Shifts!$B$2,IF($W25="",0,$W25)&gt;Shifts!$B$2,IF($X25="",0,$X25)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O25" s="54" t="n"/>
       <c r="P25" s="55">
-        <f>IF($O25&lt;&gt;"Y","",IF(OR($B25="N",$B25="DBL",$C25="N",$C25="DBL",$D25="N",$D25="DBL",$E25="N",$E25="DBL",$F25="N",$F25="DBL",$G25="N",$G25="DBL",$H25="N",$H25="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O25&lt;&gt;"Y","",IF(OR($B25="N",$B25="DBL",$C25="N",$C25="DBL",$D25="N",$D25="DBL",$E25="N",$E25="DBL",$F25="N",$F25="DBL",$G25="N",$G25="DBL",$H25="N",$H25="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R25">
@@ -4516,12 +4516,12 @@
         <v/>
       </c>
       <c r="N26">
-        <f>IF($O26="Y",IF(OR(IF($R26="",0,$R26)&gt;8,IF($S26="",0,$S26)&gt;8,IF($T26="",0,$T26)&gt;8,IF($U26="",0,$U26)&gt;8,IF($V26="",0,$V26)&gt;8,IF($W26="",0,$W26)&gt;8,IF($X26="",0,$X26)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R26="",0,$R26)&gt;Shifts!$B$2,IF($S26="",0,$S26)&gt;Shifts!$B$2,IF($T26="",0,$T26)&gt;Shifts!$B$2,IF($U26="",0,$U26)&gt;Shifts!$B$2,IF($V26="",0,$V26)&gt;Shifts!$B$2,IF($W26="",0,$W26)&gt;Shifts!$B$2,IF($X26="",0,$X26)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O26="Y",IF(OR(IF($R26="",0,$R26)&gt;8,IF($S26="",0,$S26)&gt;8,IF($T26="",0,$T26)&gt;8,IF($U26="",0,$U26)&gt;8,IF($V26="",0,$V26)&gt;8,IF($W26="",0,$W26)&gt;8,IF($X26="",0,$X26)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R26="",0,$R26)&gt;Shifts!$B$2,IF($S26="",0,$S26)&gt;Shifts!$B$2,IF($T26="",0,$T26)&gt;Shifts!$B$2,IF($U26="",0,$U26)&gt;Shifts!$B$2,IF($V26="",0,$V26)&gt;Shifts!$B$2,IF($W26="",0,$W26)&gt;Shifts!$B$2,IF($X26="",0,$X26)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O26" s="54" t="n"/>
       <c r="P26" s="55">
-        <f>IF($O26&lt;&gt;"Y","",IF(OR($B26="N",$B26="DBL",$C26="N",$C26="DBL",$D26="N",$D26="DBL",$E26="N",$E26="DBL",$F26="N",$F26="DBL",$G26="N",$G26="DBL",$H26="N",$H26="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O26&lt;&gt;"Y","",IF(OR($B26="N",$B26="DBL",$C26="N",$C26="DBL",$D26="N",$D26="DBL",$E26="N",$E26="DBL",$F26="N",$F26="DBL",$G26="N",$G26="DBL",$H26="N",$H26="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R26">
@@ -4662,12 +4662,12 @@
         <v/>
       </c>
       <c r="N27">
-        <f>IF($O27="Y",IF(OR(IF($R27="",0,$R27)&gt;8,IF($S27="",0,$S27)&gt;8,IF($T27="",0,$T27)&gt;8,IF($U27="",0,$U27)&gt;8,IF($V27="",0,$V27)&gt;8,IF($W27="",0,$W27)&gt;8,IF($X27="",0,$X27)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R27="",0,$R27)&gt;Shifts!$B$2,IF($S27="",0,$S27)&gt;Shifts!$B$2,IF($T27="",0,$T27)&gt;Shifts!$B$2,IF($U27="",0,$U27)&gt;Shifts!$B$2,IF($V27="",0,$V27)&gt;Shifts!$B$2,IF($W27="",0,$W27)&gt;Shifts!$B$2,IF($X27="",0,$X27)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O27="Y",IF(OR(IF($R27="",0,$R27)&gt;8,IF($S27="",0,$S27)&gt;8,IF($T27="",0,$T27)&gt;8,IF($U27="",0,$U27)&gt;8,IF($V27="",0,$V27)&gt;8,IF($W27="",0,$W27)&gt;8,IF($X27="",0,$X27)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R27="",0,$R27)&gt;Shifts!$B$2,IF($S27="",0,$S27)&gt;Shifts!$B$2,IF($T27="",0,$T27)&gt;Shifts!$B$2,IF($U27="",0,$U27)&gt;Shifts!$B$2,IF($V27="",0,$V27)&gt;Shifts!$B$2,IF($W27="",0,$W27)&gt;Shifts!$B$2,IF($X27="",0,$X27)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O27" s="54" t="n"/>
       <c r="P27" s="55">
-        <f>IF($O27&lt;&gt;"Y","",IF(OR($B27="N",$B27="DBL",$C27="N",$C27="DBL",$D27="N",$D27="DBL",$E27="N",$E27="DBL",$F27="N",$F27="DBL",$G27="N",$G27="DBL",$H27="N",$H27="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O27&lt;&gt;"Y","",IF(OR($B27="N",$B27="DBL",$C27="N",$C27="DBL",$D27="N",$D27="DBL",$E27="N",$E27="DBL",$F27="N",$F27="DBL",$G27="N",$G27="DBL",$H27="N",$H27="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R27">
@@ -4808,12 +4808,12 @@
         <v/>
       </c>
       <c r="N28">
-        <f>IF($O28="Y",IF(OR(IF($R28="",0,$R28)&gt;8,IF($S28="",0,$S28)&gt;8,IF($T28="",0,$T28)&gt;8,IF($U28="",0,$U28)&gt;8,IF($V28="",0,$V28)&gt;8,IF($W28="",0,$W28)&gt;8,IF($X28="",0,$X28)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R28="",0,$R28)&gt;Shifts!$B$2,IF($S28="",0,$S28)&gt;Shifts!$B$2,IF($T28="",0,$T28)&gt;Shifts!$B$2,IF($U28="",0,$U28)&gt;Shifts!$B$2,IF($V28="",0,$V28)&gt;Shifts!$B$2,IF($W28="",0,$W28)&gt;Shifts!$B$2,IF($X28="",0,$X28)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O28="Y",IF(OR(IF($R28="",0,$R28)&gt;8,IF($S28="",0,$S28)&gt;8,IF($T28="",0,$T28)&gt;8,IF($U28="",0,$U28)&gt;8,IF($V28="",0,$V28)&gt;8,IF($W28="",0,$W28)&gt;8,IF($X28="",0,$X28)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R28="",0,$R28)&gt;Shifts!$B$2,IF($S28="",0,$S28)&gt;Shifts!$B$2,IF($T28="",0,$T28)&gt;Shifts!$B$2,IF($U28="",0,$U28)&gt;Shifts!$B$2,IF($V28="",0,$V28)&gt;Shifts!$B$2,IF($W28="",0,$W28)&gt;Shifts!$B$2,IF($X28="",0,$X28)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O28" s="54" t="n"/>
       <c r="P28" s="55">
-        <f>IF($O28&lt;&gt;"Y","",IF(OR($B28="N",$B28="DBL",$C28="N",$C28="DBL",$D28="N",$D28="DBL",$E28="N",$E28="DBL",$F28="N",$F28="DBL",$G28="N",$G28="DBL",$H28="N",$H28="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O28&lt;&gt;"Y","",IF(OR($B28="N",$B28="DBL",$C28="N",$C28="DBL",$D28="N",$D28="DBL",$E28="N",$E28="DBL",$F28="N",$F28="DBL",$G28="N",$G28="DBL",$H28="N",$H28="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R28">
@@ -4954,12 +4954,12 @@
         <v/>
       </c>
       <c r="N29">
-        <f>IF($O29="Y",IF(OR(IF($R29="",0,$R29)&gt;8,IF($S29="",0,$S29)&gt;8,IF($T29="",0,$T29)&gt;8,IF($U29="",0,$U29)&gt;8,IF($V29="",0,$V29)&gt;8,IF($W29="",0,$W29)&gt;8,IF($X29="",0,$X29)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R29="",0,$R29)&gt;Shifts!$B$2,IF($S29="",0,$S29)&gt;Shifts!$B$2,IF($T29="",0,$T29)&gt;Shifts!$B$2,IF($U29="",0,$U29)&gt;Shifts!$B$2,IF($V29="",0,$V29)&gt;Shifts!$B$2,IF($W29="",0,$W29)&gt;Shifts!$B$2,IF($X29="",0,$X29)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O29="Y",IF(OR(IF($R29="",0,$R29)&gt;8,IF($S29="",0,$S29)&gt;8,IF($T29="",0,$T29)&gt;8,IF($U29="",0,$U29)&gt;8,IF($V29="",0,$V29)&gt;8,IF($W29="",0,$W29)&gt;8,IF($X29="",0,$X29)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R29="",0,$R29)&gt;Shifts!$B$2,IF($S29="",0,$S29)&gt;Shifts!$B$2,IF($T29="",0,$T29)&gt;Shifts!$B$2,IF($U29="",0,$U29)&gt;Shifts!$B$2,IF($V29="",0,$V29)&gt;Shifts!$B$2,IF($W29="",0,$W29)&gt;Shifts!$B$2,IF($X29="",0,$X29)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O29" s="54" t="n"/>
       <c r="P29" s="55">
-        <f>IF($O29&lt;&gt;"Y","",IF(OR($B29="N",$B29="DBL",$C29="N",$C29="DBL",$D29="N",$D29="DBL",$E29="N",$E29="DBL",$F29="N",$F29="DBL",$G29="N",$G29="DBL",$H29="N",$H29="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O29&lt;&gt;"Y","",IF(OR($B29="N",$B29="DBL",$C29="N",$C29="DBL",$D29="N",$D29="DBL",$E29="N",$E29="DBL",$F29="N",$F29="DBL",$G29="N",$G29="DBL",$H29="N",$H29="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R29">
@@ -5100,12 +5100,12 @@
         <v/>
       </c>
       <c r="N30">
-        <f>IF($O30="Y",IF(OR(IF($R30="",0,$R30)&gt;8,IF($S30="",0,$S30)&gt;8,IF($T30="",0,$T30)&gt;8,IF($U30="",0,$U30)&gt;8,IF($V30="",0,$V30)&gt;8,IF($W30="",0,$W30)&gt;8,IF($X30="",0,$X30)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R30="",0,$R30)&gt;Shifts!$B$2,IF($S30="",0,$S30)&gt;Shifts!$B$2,IF($T30="",0,$T30)&gt;Shifts!$B$2,IF($U30="",0,$U30)&gt;Shifts!$B$2,IF($V30="",0,$V30)&gt;Shifts!$B$2,IF($W30="",0,$W30)&gt;Shifts!$B$2,IF($X30="",0,$X30)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O30="Y",IF(OR(IF($R30="",0,$R30)&gt;8,IF($S30="",0,$S30)&gt;8,IF($T30="",0,$T30)&gt;8,IF($U30="",0,$U30)&gt;8,IF($V30="",0,$V30)&gt;8,IF($W30="",0,$W30)&gt;8,IF($X30="",0,$X30)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R30="",0,$R30)&gt;Shifts!$B$2,IF($S30="",0,$S30)&gt;Shifts!$B$2,IF($T30="",0,$T30)&gt;Shifts!$B$2,IF($U30="",0,$U30)&gt;Shifts!$B$2,IF($V30="",0,$V30)&gt;Shifts!$B$2,IF($W30="",0,$W30)&gt;Shifts!$B$2,IF($X30="",0,$X30)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O30" s="54" t="n"/>
       <c r="P30" s="55">
-        <f>IF($O30&lt;&gt;"Y","",IF(OR($B30="N",$B30="DBL",$C30="N",$C30="DBL",$D30="N",$D30="DBL",$E30="N",$E30="DBL",$F30="N",$F30="DBL",$G30="N",$G30="DBL",$H30="N",$H30="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O30&lt;&gt;"Y","",IF(OR($B30="N",$B30="DBL",$C30="N",$C30="DBL",$D30="N",$D30="DBL",$E30="N",$E30="DBL",$F30="N",$F30="DBL",$G30="N",$G30="DBL",$H30="N",$H30="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R30">
@@ -5246,12 +5246,12 @@
         <v/>
       </c>
       <c r="N31">
-        <f>IF($O31="Y",IF(OR(IF($R31="",0,$R31)&gt;8,IF($S31="",0,$S31)&gt;8,IF($T31="",0,$T31)&gt;8,IF($U31="",0,$U31)&gt;8,IF($V31="",0,$V31)&gt;8,IF($W31="",0,$W31)&gt;8,IF($X31="",0,$X31)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R31="",0,$R31)&gt;Shifts!$B$2,IF($S31="",0,$S31)&gt;Shifts!$B$2,IF($T31="",0,$T31)&gt;Shifts!$B$2,IF($U31="",0,$U31)&gt;Shifts!$B$2,IF($V31="",0,$V31)&gt;Shifts!$B$2,IF($W31="",0,$W31)&gt;Shifts!$B$2,IF($X31="",0,$X31)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O31="Y",IF(OR(IF($R31="",0,$R31)&gt;8,IF($S31="",0,$S31)&gt;8,IF($T31="",0,$T31)&gt;8,IF($U31="",0,$U31)&gt;8,IF($V31="",0,$V31)&gt;8,IF($W31="",0,$W31)&gt;8,IF($X31="",0,$X31)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R31="",0,$R31)&gt;Shifts!$B$2,IF($S31="",0,$S31)&gt;Shifts!$B$2,IF($T31="",0,$T31)&gt;Shifts!$B$2,IF($U31="",0,$U31)&gt;Shifts!$B$2,IF($V31="",0,$V31)&gt;Shifts!$B$2,IF($W31="",0,$W31)&gt;Shifts!$B$2,IF($X31="",0,$X31)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O31" s="54" t="n"/>
       <c r="P31" s="55">
-        <f>IF($O31&lt;&gt;"Y","",IF(OR($B31="N",$B31="DBL",$C31="N",$C31="DBL",$D31="N",$D31="DBL",$E31="N",$E31="DBL",$F31="N",$F31="DBL",$G31="N",$G31="DBL",$H31="N",$H31="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O31&lt;&gt;"Y","",IF(OR($B31="N",$B31="DBL",$C31="N",$C31="DBL",$D31="N",$D31="DBL",$E31="N",$E31="DBL",$F31="N",$F31="DBL",$G31="N",$G31="DBL",$H31="N",$H31="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R31">
@@ -5392,12 +5392,12 @@
         <v/>
       </c>
       <c r="N32">
-        <f>IF($O32="Y",IF(OR(IF($R32="",0,$R32)&gt;8,IF($S32="",0,$S32)&gt;8,IF($T32="",0,$T32)&gt;8,IF($U32="",0,$U32)&gt;8,IF($V32="",0,$V32)&gt;8,IF($W32="",0,$W32)&gt;8,IF($X32="",0,$X32)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R32="",0,$R32)&gt;Shifts!$B$2,IF($S32="",0,$S32)&gt;Shifts!$B$2,IF($T32="",0,$T32)&gt;Shifts!$B$2,IF($U32="",0,$U32)&gt;Shifts!$B$2,IF($V32="",0,$V32)&gt;Shifts!$B$2,IF($W32="",0,$W32)&gt;Shifts!$B$2,IF($X32="",0,$X32)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O32="Y",IF(OR(IF($R32="",0,$R32)&gt;8,IF($S32="",0,$S32)&gt;8,IF($T32="",0,$T32)&gt;8,IF($U32="",0,$U32)&gt;8,IF($V32="",0,$V32)&gt;8,IF($W32="",0,$W32)&gt;8,IF($X32="",0,$X32)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R32="",0,$R32)&gt;Shifts!$B$2,IF($S32="",0,$S32)&gt;Shifts!$B$2,IF($T32="",0,$T32)&gt;Shifts!$B$2,IF($U32="",0,$U32)&gt;Shifts!$B$2,IF($V32="",0,$V32)&gt;Shifts!$B$2,IF($W32="",0,$W32)&gt;Shifts!$B$2,IF($X32="",0,$X32)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O32" s="54" t="n"/>
       <c r="P32" s="55">
-        <f>IF($O32&lt;&gt;"Y","",IF(OR($B32="N",$B32="DBL",$C32="N",$C32="DBL",$D32="N",$D32="DBL",$E32="N",$E32="DBL",$F32="N",$F32="DBL",$G32="N",$G32="DBL",$H32="N",$H32="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O32&lt;&gt;"Y","",IF(OR($B32="N",$B32="DBL",$C32="N",$C32="DBL",$D32="N",$D32="DBL",$E32="N",$E32="DBL",$F32="N",$F32="DBL",$G32="N",$G32="DBL",$H32="N",$H32="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R32">
@@ -5538,12 +5538,12 @@
         <v/>
       </c>
       <c r="N33">
-        <f>IF($O33="Y",IF(OR(IF($R33="",0,$R33)&gt;8,IF($S33="",0,$S33)&gt;8,IF($T33="",0,$T33)&gt;8,IF($U33="",0,$U33)&gt;8,IF($V33="",0,$V33)&gt;8,IF($W33="",0,$W33)&gt;8,IF($X33="",0,$X33)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R33="",0,$R33)&gt;Shifts!$B$2,IF($S33="",0,$S33)&gt;Shifts!$B$2,IF($T33="",0,$T33)&gt;Shifts!$B$2,IF($U33="",0,$U33)&gt;Shifts!$B$2,IF($V33="",0,$V33)&gt;Shifts!$B$2,IF($W33="",0,$W33)&gt;Shifts!$B$2,IF($X33="",0,$X33)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O33="Y",IF(OR(IF($R33="",0,$R33)&gt;8,IF($S33="",0,$S33)&gt;8,IF($T33="",0,$T33)&gt;8,IF($U33="",0,$U33)&gt;8,IF($V33="",0,$V33)&gt;8,IF($W33="",0,$W33)&gt;8,IF($X33="",0,$X33)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R33="",0,$R33)&gt;Shifts!$B$2,IF($S33="",0,$S33)&gt;Shifts!$B$2,IF($T33="",0,$T33)&gt;Shifts!$B$2,IF($U33="",0,$U33)&gt;Shifts!$B$2,IF($V33="",0,$V33)&gt;Shifts!$B$2,IF($W33="",0,$W33)&gt;Shifts!$B$2,IF($X33="",0,$X33)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O33" s="54" t="n"/>
       <c r="P33" s="55">
-        <f>IF($O33&lt;&gt;"Y","",IF(OR($B33="N",$B33="DBL",$C33="N",$C33="DBL",$D33="N",$D33="DBL",$E33="N",$E33="DBL",$F33="N",$F33="DBL",$G33="N",$G33="DBL",$H33="N",$H33="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O33&lt;&gt;"Y","",IF(OR($B33="N",$B33="DBL",$C33="N",$C33="DBL",$D33="N",$D33="DBL",$E33="N",$E33="DBL",$F33="N",$F33="DBL",$G33="N",$G33="DBL",$H33="N",$H33="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R33">
@@ -5684,12 +5684,12 @@
         <v/>
       </c>
       <c r="N34">
-        <f>IF($O34="Y",IF(OR(IF($R34="",0,$R34)&gt;8,IF($S34="",0,$S34)&gt;8,IF($T34="",0,$T34)&gt;8,IF($U34="",0,$U34)&gt;8,IF($V34="",0,$V34)&gt;8,IF($W34="",0,$W34)&gt;8,IF($X34="",0,$X34)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R34="",0,$R34)&gt;Shifts!$B$2,IF($S34="",0,$S34)&gt;Shifts!$B$2,IF($T34="",0,$T34)&gt;Shifts!$B$2,IF($U34="",0,$U34)&gt;Shifts!$B$2,IF($V34="",0,$V34)&gt;Shifts!$B$2,IF($W34="",0,$W34)&gt;Shifts!$B$2,IF($X34="",0,$X34)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O34="Y",IF(OR(IF($R34="",0,$R34)&gt;8,IF($S34="",0,$S34)&gt;8,IF($T34="",0,$T34)&gt;8,IF($U34="",0,$U34)&gt;8,IF($V34="",0,$V34)&gt;8,IF($W34="",0,$W34)&gt;8,IF($X34="",0,$X34)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R34="",0,$R34)&gt;Shifts!$B$2,IF($S34="",0,$S34)&gt;Shifts!$B$2,IF($T34="",0,$T34)&gt;Shifts!$B$2,IF($U34="",0,$U34)&gt;Shifts!$B$2,IF($V34="",0,$V34)&gt;Shifts!$B$2,IF($W34="",0,$W34)&gt;Shifts!$B$2,IF($X34="",0,$X34)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O34" s="54" t="n"/>
       <c r="P34" s="55">
-        <f>IF($O34&lt;&gt;"Y","",IF(OR($B34="N",$B34="DBL",$C34="N",$C34="DBL",$D34="N",$D34="DBL",$E34="N",$E34="DBL",$F34="N",$F34="DBL",$G34="N",$G34="DBL",$H34="N",$H34="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O34&lt;&gt;"Y","",IF(OR($B34="N",$B34="DBL",$C34="N",$C34="DBL",$D34="N",$D34="DBL",$E34="N",$E34="DBL",$F34="N",$F34="DBL",$G34="N",$G34="DBL",$H34="N",$H34="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R34">
@@ -5830,12 +5830,12 @@
         <v/>
       </c>
       <c r="N35">
-        <f>IF($O35="Y",IF(OR(IF($R35="",0,$R35)&gt;8,IF($S35="",0,$S35)&gt;8,IF($T35="",0,$T35)&gt;8,IF($U35="",0,$U35)&gt;8,IF($V35="",0,$V35)&gt;8,IF($W35="",0,$W35)&gt;8,IF($X35="",0,$X35)&gt;8),"⛔ shift &gt; 8 h (MINOR)",""),IF(OR(IF($R35="",0,$R35)&gt;Shifts!$B$2,IF($S35="",0,$S35)&gt;Shifts!$B$2,IF($T35="",0,$T35)&gt;Shifts!$B$2,IF($U35="",0,$U35)&gt;Shifts!$B$2,IF($V35="",0,$V35)&gt;Shifts!$B$2,IF($W35="",0,$W35)&gt;Shifts!$B$2,IF($X35="",0,$X35)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
+        <f>IF($O35="Y",IF(OR(IF($R35="",0,$R35)&gt;8,IF($S35="",0,$S35)&gt;8,IF($T35="",0,$T35)&gt;8,IF($U35="",0,$U35)&gt;8,IF($V35="",0,$V35)&gt;8,IF($W35="",0,$W35)&gt;8,IF($X35="",0,$X35)&gt;8),"⛔ &gt; 8 h (under-16 cap)",""),IF(OR(IF($R35="",0,$R35)&gt;Shifts!$B$2,IF($S35="",0,$S35)&gt;Shifts!$B$2,IF($T35="",0,$T35)&gt;Shifts!$B$2,IF($U35="",0,$U35)&gt;Shifts!$B$2,IF($V35="",0,$V35)&gt;Shifts!$B$2,IF($W35="",0,$W35)&gt;Shifts!$B$2,IF($X35="",0,$X35)&gt;Shifts!$B$2),"⛔ shift &gt; "&amp;Shifts!$B$2&amp;" h",""))</f>
         <v/>
       </c>
       <c r="O35" s="54" t="n"/>
       <c r="P35" s="55">
-        <f>IF($O35&lt;&gt;"Y","",IF(OR($B35="N",$B35="DBL",$C35="N",$C35="DBL",$D35="N",$D35="DBL",$E35="N",$E35="DBL",$F35="N",$F35="DBL",$G35="N",$G35="DBL",$H35="N",$H35="DBL"),"⛔ MINOR: no night or double shifts (29 CFR 570.35)","⚠ minor: check federal and state hour limits"))</f>
+        <f>IF($O35&lt;&gt;"Y","",IF(OR($B35="N",$B35="DBL",$C35="N",$C35="DBL",$D35="N",$D35="DBL",$E35="N",$E35="DBL",$F35="N",$F35="DBL",$G35="N",$G35="DBL",$H35="N",$H35="DBL"),"⛔ UNDER 16: no work after 7 PM (9 PM Jun 1–Labor Day), 29 CFR 570.35; 16-17: state law","⚠ Minor: under 16, PM/SP end after 7 PM — check 570.35 + state law"))</f>
         <v/>
       </c>
       <c r="R35">
@@ -6052,10 +6052,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="O6:O35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Type Y or N." promptTitle="grupoA-v2 · Invalid value" prompt="Type Y if this person is UNDER 18. File 07 flags it in its &quot;Alert&quot; column once you enter the date of birth. With Y, the long-shift alert drops to 8 h and fires on a night (N) or double (DBL) shift: child labor rules, 29 CFR 570." type="list" errorStyle="stop">
+    <dataValidation sqref="O6:O35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Type Y or N." promptTitle="Minor (under 18)? Y/N" prompt="Type Y if this person is UNDER 18 (file 07 flags it once you enter the date of birth). With Y, N flags shifts over 8 h and P turns red on N or DBL, amber otherwise. Under 16: no work after 7 PM (9 PM in summer), 29 CFR 570.35. 16-17: state law." type="list" errorStyle="stop">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="B6:H35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes. They are the same in the weekly and the monthly schedule, and the hours and alerts come from them: an invented code counts 0 h without warning." promptTitle="kitgp-v2 · Invalid shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
+    <dataValidation sqref="B6:H35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes. They are the same in the weekly and the monthly schedule, and the hours and alerts come from them: an invented code counts 0 h without warning." promptTitle="Shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
       <formula1>"AM,PM,N,SP,DBL,OFF,V,S"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="J169" s="27" t="inlineStr">
         <is>
-          <t>Average-hours alert</t>
+          <t>Average alert (planning only)</t>
         </is>
       </c>
     </row>
@@ -11067,19 +11067,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="B5:H34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="grupoA-v2 · Invalid shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
+    <dataValidation sqref="B5:H34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="Shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
       <formula1>"AM,PM,N,SP,DBL,OFF,V,S"</formula1>
     </dataValidation>
-    <dataValidation sqref="B38:H67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="grupoA-v2 · Invalid shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
+    <dataValidation sqref="B38:H67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="Shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
       <formula1>"AM,PM,N,SP,DBL,OFF,V,S"</formula1>
     </dataValidation>
-    <dataValidation sqref="B71:H100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="grupoA-v2 · Invalid shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
+    <dataValidation sqref="B71:H100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="Shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
       <formula1>"AM,PM,N,SP,DBL,OFF,V,S"</formula1>
     </dataValidation>
-    <dataValidation sqref="B104:H133" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="grupoA-v2 · Invalid shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
+    <dataValidation sqref="B104:H133" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="Shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
       <formula1>"AM,PM,N,SP,DBL,OFF,V,S"</formula1>
     </dataValidation>
-    <dataValidation sqref="B137:H166" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="grupoA-v2 · Invalid shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
+    <dataValidation sqref="B137:H166" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid shift code" error="Use one of the 8 kit codes: they are the same as in the &quot;Weekly Schedule&quot;, and the hours and alerts come from them." promptTitle="Shift code" prompt="Shift codes: AM=AM shift · PM=PM shift · N=Night · SP=Split · DBL=Double · OFF=Day off · V=Vacation/PTO · S=Sick." type="list" errorStyle="stop">
       <formula1>"AM,PM,N,SP,DBL,OFF,V,S"</formula1>
     </dataValidation>
   </dataValidations>
